--- a/2023/新闻数量及词频(2023).xlsx
+++ b/2023/新闻数量及词频(2023).xlsx
@@ -1,17 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15680" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="中新网" sheetId="1" r:id="rId1"/>
     <sheet name="人民网" sheetId="2" r:id="rId2"/>
     <sheet name="百度新闻" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -147,6 +160,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>2023</t>
     </r>
     <r>
@@ -176,6 +194,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>2023</t>
     </r>
     <r>
@@ -205,6 +228,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>2023</t>
     </r>
     <r>
@@ -234,6 +262,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>2023</t>
     </r>
     <r>
@@ -263,6 +296,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>2023</t>
     </r>
     <r>
@@ -292,6 +330,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>2023</t>
     </r>
     <r>
@@ -321,6 +364,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>2023</t>
     </r>
     <r>
@@ -350,6 +398,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>2023</t>
     </r>
     <r>
@@ -379,6 +432,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>2023</t>
     </r>
     <r>
@@ -408,6 +466,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>2023</t>
     </r>
     <r>
@@ -439,12 +502,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -523,28 +586,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -553,9 +594,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -576,24 +617,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -608,10 +634,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -623,9 +649,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -639,8 +672,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -648,6 +682,21 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -661,7 +710,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -686,37 +749,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -728,79 +791,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -818,13 +809,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -836,37 +881,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -877,15 +940,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -900,6 +954,54 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -919,26 +1021,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -953,181 +1040,157 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1143,6 +1206,9 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1152,13 +1218,7 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1170,13 +1230,13 @@
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1194,54 +1254,54 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
     <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
     <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1511,99 +1571,99 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AA21"/>
-  <sheetFormatPr defaultColWidth="15.2307692307692" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="15.2300884955752" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="23.3076923076923" style="12" customWidth="1"/>
+    <col min="1" max="1" width="23.3097345132743" style="11" customWidth="1"/>
     <col min="2" max="4" width="15" style="3"/>
-    <col min="5" max="5" width="17.7692307692308" style="3" customWidth="1"/>
+    <col min="5" max="5" width="17.7699115044248" style="3" customWidth="1"/>
     <col min="6" max="16384" width="15" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="16" customFormat="1" ht="23.2" spans="1:27">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="16" t="s">
+    <row r="1" s="13" customFormat="1" ht="20.25" spans="1:27">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="P1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="Q1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="16" t="s">
+      <c r="R1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="16" t="s">
+      <c r="S1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="16" t="s">
+      <c r="T1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="16" t="s">
+      <c r="U1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="16" t="s">
+      <c r="V1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="16" t="s">
+      <c r="W1" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="16" t="s">
+      <c r="X1" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="16" t="s">
+      <c r="Y1" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="16" t="s">
+      <c r="Z1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="16" t="s">
+      <c r="AA1" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" s="3" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A2" s="7" t="s">
+    <row r="2" s="3" customFormat="1" ht="20.25" spans="1:27">
+      <c r="A2" s="8" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="3">
@@ -1685,8 +1745,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A3" s="7" t="s">
+    <row r="3" s="3" customFormat="1" ht="20.25" spans="1:27">
+      <c r="A3" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B3" s="3">
@@ -1768,8 +1828,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" s="3" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A4" s="7" t="s">
+    <row r="4" s="3" customFormat="1" ht="20.25" spans="1:27">
+      <c r="A4" s="8" t="s">
         <v>29</v>
       </c>
       <c r="B4" s="3">
@@ -1851,8 +1911,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" s="3" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A5" s="7" t="s">
+    <row r="5" s="3" customFormat="1" ht="20.25" spans="1:27">
+      <c r="A5" s="8" t="s">
         <v>30</v>
       </c>
       <c r="B5" s="3">
@@ -1934,8 +1994,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A6" s="7" t="s">
+    <row r="6" s="3" customFormat="1" ht="20.25" spans="1:27">
+      <c r="A6" s="8" t="s">
         <v>31</v>
       </c>
       <c r="B6" s="3">
@@ -2017,8 +2077,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A7" s="7" t="s">
+    <row r="7" s="3" customFormat="1" ht="20.25" spans="1:27">
+      <c r="A7" s="8" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="3">
@@ -2100,8 +2160,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A8" s="7" t="s">
+    <row r="8" s="3" customFormat="1" ht="20.25" spans="1:27">
+      <c r="A8" s="8" t="s">
         <v>33</v>
       </c>
       <c r="B8" s="3">
@@ -2183,8 +2243,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A9" s="7" t="s">
+    <row r="9" s="3" customFormat="1" ht="20.25" spans="1:27">
+      <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B9" s="3">
@@ -2266,8 +2326,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" s="3" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A10" s="7" t="s">
+    <row r="10" s="3" customFormat="1" ht="20.25" spans="1:27">
+      <c r="A10" s="8" t="s">
         <v>35</v>
       </c>
       <c r="B10" s="3">
@@ -2349,8 +2409,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A11" s="7" t="s">
+    <row r="11" s="3" customFormat="1" ht="20.25" spans="1:27">
+      <c r="A11" s="8" t="s">
         <v>36</v>
       </c>
       <c r="B11" s="3">
@@ -2432,8 +2492,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A12" s="7" t="s">
+    <row r="12" s="3" customFormat="1" ht="20.25" spans="1:27">
+      <c r="A12" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B12" s="3">
@@ -2515,8 +2575,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" s="3" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A13" s="7" t="s">
+    <row r="13" s="3" customFormat="1" ht="20.25" spans="1:27">
+      <c r="A13" s="8" t="s">
         <v>38</v>
       </c>
       <c r="B13" s="3">
@@ -2598,16 +2658,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" s="3" customFormat="1" ht="19.6" spans="1:1">
-      <c r="A14" s="19"/>
+    <row r="14" s="3" customFormat="1" ht="20.25" spans="1:27">
+      <c r="A14" s="18"/>
     </row>
-    <row r="20" s="3" customFormat="1" ht="19.6" spans="1:5">
-      <c r="A20" s="12"/>
-      <c r="E20" s="20"/>
+    <row r="20" s="3" customFormat="1" ht="20.25" spans="1:5">
+      <c r="A20" s="11"/>
+      <c r="E20" s="19"/>
     </row>
-    <row r="21" s="3" customFormat="1" ht="19.6" spans="1:5">
-      <c r="A21" s="12"/>
-      <c r="E21" s="20"/>
+    <row r="21" s="3" customFormat="1" ht="20.25" spans="1:5">
+      <c r="A21" s="11"/>
+      <c r="E21" s="19"/>
     </row>
   </sheetData>
   <sortState ref="A2:AA21">
@@ -2622,16 +2682,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AA13"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9.23008849557522" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="14.3076923076923" style="11" customWidth="1"/>
-    <col min="2" max="25" width="9.23076923076923" style="2"/>
-    <col min="26" max="27" width="15" style="12"/>
-    <col min="28" max="16384" width="9.23076923076923" style="2"/>
+    <col min="1" max="1" width="14.3097345132743" style="10" customWidth="1"/>
+    <col min="2" max="25" width="9.23008849557522" style="2"/>
+    <col min="26" max="27" width="15" style="11"/>
+    <col min="28" max="16384" width="9.23008849557522" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="1" ht="24" spans="1:27">
-      <c r="A1" s="13" t="s">
+    <row r="1" s="9" customFormat="1" ht="20.25" spans="1:27">
+      <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="9" t="s">
@@ -2706,14 +2766,14 @@
       <c r="Y1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="16" t="s">
+      <c r="Z1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="16" t="s">
+      <c r="AA1" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" s="10" customFormat="1" ht="19.6" spans="1:27">
+    <row r="2" s="2" customFormat="1" ht="20.6" spans="1:27">
       <c r="A2" s="14" t="s">
         <v>27</v>
       </c>
@@ -2789,15 +2849,15 @@
       <c r="Y2" s="15">
         <v>3</v>
       </c>
-      <c r="Z2" s="17">
+      <c r="Z2" s="16">
         <v>9</v>
       </c>
-      <c r="AA2" s="17">
+      <c r="AA2" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="3" s="10" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A3" s="5" t="s">
+    <row r="3" s="2" customFormat="1" ht="20.6" spans="1:27">
+      <c r="A3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B3" s="15">
@@ -2879,8 +2939,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" s="10" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A4" s="5" t="s">
+    <row r="4" s="2" customFormat="1" ht="20.6" spans="1:27">
+      <c r="A4" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B4" s="15">
@@ -2962,8 +3022,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" s="10" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A5" s="5" t="s">
+    <row r="5" s="2" customFormat="1" ht="20.6" spans="1:27">
+      <c r="A5" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B5" s="15">
@@ -3045,7 +3105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" s="10" customFormat="1" ht="19.6" spans="1:27">
+    <row r="6" s="2" customFormat="1" ht="20.6" spans="1:27">
       <c r="A6" s="14" t="s">
         <v>31</v>
       </c>
@@ -3121,15 +3181,15 @@
       <c r="Y6" s="15">
         <v>21</v>
       </c>
-      <c r="Z6" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="17">
+      <c r="Z6" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="7" s="10" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A7" s="5" t="s">
+    <row r="7" s="2" customFormat="1" ht="20.6" spans="1:27">
+      <c r="A7" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="15">
@@ -3211,8 +3271,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" s="10" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A8" s="5" t="s">
+    <row r="8" s="2" customFormat="1" ht="20.6" spans="1:27">
+      <c r="A8" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B8" s="15">
@@ -3294,8 +3354,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" s="10" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A9" s="5" t="s">
+    <row r="9" s="2" customFormat="1" ht="20.6" spans="1:27">
+      <c r="A9" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B9" s="15">
@@ -3377,8 +3437,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" s="10" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A10" s="5" t="s">
+    <row r="10" s="2" customFormat="1" ht="20.6" spans="1:27">
+      <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B10" s="15">
@@ -3460,7 +3520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" s="10" customFormat="1" ht="19.6" spans="1:27">
+    <row r="11" s="2" customFormat="1" ht="20.6" spans="1:27">
       <c r="A11" s="14" t="s">
         <v>36</v>
       </c>
@@ -3536,15 +3596,15 @@
       <c r="Y11" s="15">
         <v>86</v>
       </c>
-      <c r="Z11" s="17">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="17">
+      <c r="Z11" s="16">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="12" s="10" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A12" s="5" t="s">
+    <row r="12" s="2" customFormat="1" ht="20.6" spans="1:27">
+      <c r="A12" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B12" s="15">
@@ -3626,8 +3686,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" s="10" customFormat="1" ht="19.6" spans="1:27">
-      <c r="A13" s="5" t="s">
+    <row r="13" s="2" customFormat="1" ht="20.6" spans="1:27">
+      <c r="A13" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B13" s="15">
@@ -3722,14 +3782,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AA11"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9.23008849557522" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="20.1923076923077" style="2" customWidth="1"/>
-    <col min="2" max="25" width="13.6923076923077" customWidth="1"/>
-    <col min="26" max="27" width="13.6923076923077" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.1946902654867" style="2" customWidth="1"/>
+    <col min="2" max="25" width="13.6902654867257" customWidth="1"/>
+    <col min="26" max="27" width="13.6902654867257" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="23.2" spans="1:27">
+    <row r="1" s="1" customFormat="1" ht="20.25" spans="1:27">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3805,87 +3865,87 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="Z1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AA1" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" ht="24" spans="1:27">
-      <c r="A2" s="5" t="s">
+    <row r="2" ht="20.65" spans="1:27">
+      <c r="A2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="7">
         <v>3</v>
       </c>
-      <c r="C2" s="6">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6">
+      <c r="C2" s="7">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7">
         <v>16</v>
       </c>
-      <c r="E2" s="6">
-        <v>0</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0</v>
-      </c>
-      <c r="G2" s="6">
-        <v>1</v>
-      </c>
-      <c r="H2" s="6">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6">
-        <v>1</v>
-      </c>
-      <c r="J2" s="6">
-        <v>0</v>
-      </c>
-      <c r="K2" s="6">
-        <v>1</v>
-      </c>
-      <c r="L2" s="6">
+      <c r="E2" s="7">
+        <v>0</v>
+      </c>
+      <c r="F2" s="7">
+        <v>0</v>
+      </c>
+      <c r="G2" s="7">
+        <v>1</v>
+      </c>
+      <c r="H2" s="7">
+        <v>0</v>
+      </c>
+      <c r="I2" s="7">
+        <v>1</v>
+      </c>
+      <c r="J2" s="7">
+        <v>0</v>
+      </c>
+      <c r="K2" s="7">
+        <v>1</v>
+      </c>
+      <c r="L2" s="7">
         <v>11</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="7">
         <v>14</v>
       </c>
-      <c r="N2" s="6">
-        <v>0</v>
-      </c>
-      <c r="O2" s="6">
-        <v>0</v>
-      </c>
-      <c r="P2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="6">
-        <v>0</v>
-      </c>
-      <c r="R2" s="6">
-        <v>0</v>
-      </c>
-      <c r="S2" s="6">
-        <v>0</v>
-      </c>
-      <c r="T2" s="6">
+      <c r="N2" s="7">
+        <v>0</v>
+      </c>
+      <c r="O2" s="7">
+        <v>0</v>
+      </c>
+      <c r="P2" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>0</v>
+      </c>
+      <c r="S2" s="7">
+        <v>0</v>
+      </c>
+      <c r="T2" s="7">
         <v>3</v>
       </c>
-      <c r="U2" s="6">
-        <v>0</v>
-      </c>
-      <c r="V2" s="6">
-        <v>0</v>
-      </c>
-      <c r="W2" s="6">
-        <v>0</v>
-      </c>
-      <c r="X2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="6">
+      <c r="U2" s="7">
+        <v>0</v>
+      </c>
+      <c r="V2" s="7">
+        <v>0</v>
+      </c>
+      <c r="W2" s="7">
+        <v>0</v>
+      </c>
+      <c r="X2" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="7">
         <v>0</v>
       </c>
       <c r="Z2" s="3">
@@ -3895,80 +3955,80 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="24" spans="1:27">
-      <c r="A3" s="5" t="s">
+    <row r="3" ht="20.65" spans="1:27">
+      <c r="A3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6">
-        <v>0</v>
-      </c>
-      <c r="E3" s="6">
-        <v>0</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6">
-        <v>0</v>
-      </c>
-      <c r="K3" s="6">
-        <v>0</v>
-      </c>
-      <c r="L3" s="6">
-        <v>0</v>
-      </c>
-      <c r="M3" s="6">
-        <v>0</v>
-      </c>
-      <c r="N3" s="6">
-        <v>0</v>
-      </c>
-      <c r="O3" s="6">
-        <v>0</v>
-      </c>
-      <c r="P3" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="6">
-        <v>0</v>
-      </c>
-      <c r="R3" s="6">
-        <v>0</v>
-      </c>
-      <c r="S3" s="6">
-        <v>0</v>
-      </c>
-      <c r="T3" s="6">
-        <v>0</v>
-      </c>
-      <c r="U3" s="6">
-        <v>0</v>
-      </c>
-      <c r="V3" s="6">
-        <v>0</v>
-      </c>
-      <c r="W3" s="6">
-        <v>0</v>
-      </c>
-      <c r="X3" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="6">
+      <c r="B3" s="7">
+        <v>1</v>
+      </c>
+      <c r="C3" s="7">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7">
+        <v>0</v>
+      </c>
+      <c r="E3" s="7">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7">
+        <v>0</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7">
+        <v>0</v>
+      </c>
+      <c r="I3" s="7">
+        <v>0</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0</v>
+      </c>
+      <c r="K3" s="7">
+        <v>0</v>
+      </c>
+      <c r="L3" s="7">
+        <v>0</v>
+      </c>
+      <c r="M3" s="7">
+        <v>0</v>
+      </c>
+      <c r="N3" s="7">
+        <v>0</v>
+      </c>
+      <c r="O3" s="7">
+        <v>0</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7">
+        <v>0</v>
+      </c>
+      <c r="S3" s="7">
+        <v>0</v>
+      </c>
+      <c r="T3" s="7">
+        <v>0</v>
+      </c>
+      <c r="U3" s="7">
+        <v>0</v>
+      </c>
+      <c r="V3" s="7">
+        <v>0</v>
+      </c>
+      <c r="W3" s="7">
+        <v>0</v>
+      </c>
+      <c r="X3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="7">
         <v>0</v>
       </c>
       <c r="Z3" s="3">
@@ -3978,80 +4038,80 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" ht="24" spans="1:27">
-      <c r="A4" s="5" t="s">
+    <row r="4" ht="20.65" spans="1:27">
+      <c r="A4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>5</v>
       </c>
-      <c r="C4" s="6">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6">
-        <v>2</v>
-      </c>
-      <c r="E4" s="6">
-        <v>2</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6">
-        <v>0</v>
-      </c>
-      <c r="K4" s="6">
-        <v>0</v>
-      </c>
-      <c r="L4" s="6">
-        <v>1</v>
-      </c>
-      <c r="M4" s="6">
+      <c r="C4" s="7">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <v>2</v>
+      </c>
+      <c r="E4" s="7">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0</v>
+      </c>
+      <c r="K4" s="7">
+        <v>0</v>
+      </c>
+      <c r="L4" s="7">
+        <v>1</v>
+      </c>
+      <c r="M4" s="7">
         <v>6</v>
       </c>
-      <c r="N4" s="6">
-        <v>0</v>
-      </c>
-      <c r="O4" s="6">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6">
-        <v>0</v>
-      </c>
-      <c r="S4" s="6">
-        <v>0</v>
-      </c>
-      <c r="T4" s="6">
-        <v>2</v>
-      </c>
-      <c r="U4" s="6">
-        <v>0</v>
-      </c>
-      <c r="V4" s="6">
-        <v>0</v>
-      </c>
-      <c r="W4" s="6">
-        <v>0</v>
-      </c>
-      <c r="X4" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="6">
+      <c r="N4" s="7">
+        <v>0</v>
+      </c>
+      <c r="O4" s="7">
+        <v>0</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="7">
+        <v>0</v>
+      </c>
+      <c r="S4" s="7">
+        <v>0</v>
+      </c>
+      <c r="T4" s="7">
+        <v>2</v>
+      </c>
+      <c r="U4" s="7">
+        <v>0</v>
+      </c>
+      <c r="V4" s="7">
+        <v>0</v>
+      </c>
+      <c r="W4" s="7">
+        <v>0</v>
+      </c>
+      <c r="X4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="7">
         <v>2</v>
       </c>
       <c r="Z4" s="3">
@@ -4061,80 +4121,80 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="24" spans="1:27">
-      <c r="A5" s="7" t="s">
+    <row r="5" ht="20.25" spans="1:27">
+      <c r="A5" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="6">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6">
-        <v>0</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6">
-        <v>1</v>
-      </c>
-      <c r="I5" s="6">
-        <v>0</v>
-      </c>
-      <c r="J5" s="6">
-        <v>0</v>
-      </c>
-      <c r="K5" s="6">
-        <v>0</v>
-      </c>
-      <c r="L5" s="6">
-        <v>0</v>
-      </c>
-      <c r="M5" s="6">
-        <v>0</v>
-      </c>
-      <c r="N5" s="6">
-        <v>0</v>
-      </c>
-      <c r="O5" s="6">
-        <v>0</v>
-      </c>
-      <c r="P5" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="6">
-        <v>0</v>
-      </c>
-      <c r="R5" s="6">
-        <v>0</v>
-      </c>
-      <c r="S5" s="6">
-        <v>0</v>
-      </c>
-      <c r="T5" s="6">
-        <v>0</v>
-      </c>
-      <c r="U5" s="6">
-        <v>0</v>
-      </c>
-      <c r="V5" s="6">
-        <v>0</v>
-      </c>
-      <c r="W5" s="6">
-        <v>0</v>
-      </c>
-      <c r="X5" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="6">
+      <c r="B5" s="7">
+        <v>1</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0</v>
+      </c>
+      <c r="K5" s="7">
+        <v>0</v>
+      </c>
+      <c r="L5" s="7">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7">
+        <v>0</v>
+      </c>
+      <c r="O5" s="7">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7">
+        <v>0</v>
+      </c>
+      <c r="S5" s="7">
+        <v>0</v>
+      </c>
+      <c r="T5" s="7">
+        <v>0</v>
+      </c>
+      <c r="U5" s="7">
+        <v>0</v>
+      </c>
+      <c r="V5" s="7">
+        <v>0</v>
+      </c>
+      <c r="W5" s="7">
+        <v>0</v>
+      </c>
+      <c r="X5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="7">
         <v>0</v>
       </c>
       <c r="Z5" s="3">
@@ -4144,80 +4204,80 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="24" spans="1:27">
-      <c r="A6" s="7" t="s">
+    <row r="6" ht="20.25" spans="1:27">
+      <c r="A6" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="6">
-        <v>2</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0</v>
-      </c>
-      <c r="D6" s="6">
-        <v>2</v>
-      </c>
-      <c r="E6" s="6">
+      <c r="B6" s="7">
+        <v>2</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
+        <v>2</v>
+      </c>
+      <c r="E6" s="7">
         <v>3</v>
       </c>
-      <c r="F6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
+      <c r="F6" s="7">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
         <v>14</v>
       </c>
-      <c r="I6" s="6">
-        <v>2</v>
-      </c>
-      <c r="J6" s="6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="6">
+      <c r="I6" s="7">
+        <v>2</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7">
         <v>4</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="7">
         <v>9</v>
       </c>
-      <c r="N6" s="6">
-        <v>0</v>
-      </c>
-      <c r="O6" s="6">
-        <v>2</v>
-      </c>
-      <c r="P6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>2</v>
-      </c>
-      <c r="R6" s="6">
-        <v>2</v>
-      </c>
-      <c r="S6" s="6">
-        <v>0</v>
-      </c>
-      <c r="T6" s="6">
-        <v>0</v>
-      </c>
-      <c r="U6" s="6">
-        <v>0</v>
-      </c>
-      <c r="V6" s="6">
-        <v>2</v>
-      </c>
-      <c r="W6" s="6">
-        <v>0</v>
-      </c>
-      <c r="X6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="6">
+      <c r="N6" s="7">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7">
+        <v>2</v>
+      </c>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>2</v>
+      </c>
+      <c r="R6" s="7">
+        <v>2</v>
+      </c>
+      <c r="S6" s="7">
+        <v>0</v>
+      </c>
+      <c r="T6" s="7">
+        <v>0</v>
+      </c>
+      <c r="U6" s="7">
+        <v>0</v>
+      </c>
+      <c r="V6" s="7">
+        <v>2</v>
+      </c>
+      <c r="W6" s="7">
+        <v>0</v>
+      </c>
+      <c r="X6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="7">
         <v>2</v>
       </c>
       <c r="Z6" s="3">
@@ -4227,80 +4287,80 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="24" spans="1:27">
-      <c r="A7" s="7" t="s">
+    <row r="7" ht="20.25" spans="1:27">
+      <c r="A7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="6">
-        <v>1</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="B7" s="7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
         <v>7</v>
       </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6">
-        <v>1</v>
-      </c>
-      <c r="H7" s="6">
+      <c r="E7" s="7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7">
         <v>6</v>
       </c>
-      <c r="I7" s="6">
-        <v>1</v>
-      </c>
-      <c r="J7" s="6">
-        <v>0</v>
-      </c>
-      <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="6">
+      <c r="I7" s="7">
+        <v>1</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7">
         <v>5</v>
       </c>
-      <c r="M7" s="6">
-        <v>2</v>
-      </c>
-      <c r="N7" s="6">
-        <v>0</v>
-      </c>
-      <c r="O7" s="6">
-        <v>1</v>
-      </c>
-      <c r="P7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6">
-        <v>2</v>
-      </c>
-      <c r="S7" s="6">
-        <v>1</v>
-      </c>
-      <c r="T7" s="6">
-        <v>2</v>
-      </c>
-      <c r="U7" s="6">
-        <v>2</v>
-      </c>
-      <c r="V7" s="6">
-        <v>1</v>
-      </c>
-      <c r="W7" s="6">
-        <v>0</v>
-      </c>
-      <c r="X7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="6">
+      <c r="M7" s="7">
+        <v>2</v>
+      </c>
+      <c r="N7" s="7">
+        <v>0</v>
+      </c>
+      <c r="O7" s="7">
+        <v>1</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
+        <v>2</v>
+      </c>
+      <c r="S7" s="7">
+        <v>1</v>
+      </c>
+      <c r="T7" s="7">
+        <v>2</v>
+      </c>
+      <c r="U7" s="7">
+        <v>2</v>
+      </c>
+      <c r="V7" s="7">
+        <v>1</v>
+      </c>
+      <c r="W7" s="7">
+        <v>0</v>
+      </c>
+      <c r="X7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="7">
         <v>0</v>
       </c>
       <c r="Z7" s="3">
@@ -4310,80 +4370,80 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="24" spans="1:27">
-      <c r="A8" s="7" t="s">
+    <row r="8" ht="20.25" spans="1:27">
+      <c r="A8" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>7</v>
       </c>
-      <c r="C8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6">
-        <v>0</v>
-      </c>
-      <c r="L8" s="6">
-        <v>1</v>
-      </c>
-      <c r="M8" s="6">
-        <v>0</v>
-      </c>
-      <c r="N8" s="6">
-        <v>0</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>0</v>
-      </c>
-      <c r="R8" s="6">
-        <v>0</v>
-      </c>
-      <c r="S8" s="6">
-        <v>0</v>
-      </c>
-      <c r="T8" s="6">
-        <v>0</v>
-      </c>
-      <c r="U8" s="6">
-        <v>0</v>
-      </c>
-      <c r="V8" s="6">
-        <v>0</v>
-      </c>
-      <c r="W8" s="6">
-        <v>0</v>
-      </c>
-      <c r="X8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="6">
+      <c r="C8" s="7">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>1</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7">
+        <v>1</v>
+      </c>
+      <c r="M8" s="7">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7">
+        <v>0</v>
+      </c>
+      <c r="O8" s="7">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
+        <v>0</v>
+      </c>
+      <c r="S8" s="7">
+        <v>0</v>
+      </c>
+      <c r="T8" s="7">
+        <v>0</v>
+      </c>
+      <c r="U8" s="7">
+        <v>0</v>
+      </c>
+      <c r="V8" s="7">
+        <v>0</v>
+      </c>
+      <c r="W8" s="7">
+        <v>0</v>
+      </c>
+      <c r="X8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="7">
         <v>0</v>
       </c>
       <c r="Z8" s="3">
@@ -4393,80 +4453,80 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="24" spans="1:27">
-      <c r="A9" s="5" t="s">
+    <row r="9" ht="20.65" spans="1:27">
+      <c r="A9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="6">
-        <v>2</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="B9" s="7">
+        <v>2</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7">
         <v>6</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <v>3</v>
       </c>
-      <c r="F9" s="6">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6">
-        <v>0</v>
-      </c>
-      <c r="K9" s="6">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6">
-        <v>2</v>
-      </c>
-      <c r="M9" s="6">
-        <v>0</v>
-      </c>
-      <c r="N9" s="6">
-        <v>0</v>
-      </c>
-      <c r="O9" s="6">
-        <v>0</v>
-      </c>
-      <c r="P9" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>0</v>
-      </c>
-      <c r="R9" s="6">
-        <v>0</v>
-      </c>
-      <c r="S9" s="6">
-        <v>0</v>
-      </c>
-      <c r="T9" s="6">
-        <v>1</v>
-      </c>
-      <c r="U9" s="6">
-        <v>0</v>
-      </c>
-      <c r="V9" s="6">
-        <v>0</v>
-      </c>
-      <c r="W9" s="6">
-        <v>0</v>
-      </c>
-      <c r="X9" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="6">
+      <c r="F9" s="7">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0</v>
+      </c>
+      <c r="K9" s="7">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7">
+        <v>2</v>
+      </c>
+      <c r="M9" s="7">
+        <v>0</v>
+      </c>
+      <c r="N9" s="7">
+        <v>0</v>
+      </c>
+      <c r="O9" s="7">
+        <v>0</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
+        <v>0</v>
+      </c>
+      <c r="S9" s="7">
+        <v>0</v>
+      </c>
+      <c r="T9" s="7">
+        <v>1</v>
+      </c>
+      <c r="U9" s="7">
+        <v>0</v>
+      </c>
+      <c r="V9" s="7">
+        <v>0</v>
+      </c>
+      <c r="W9" s="7">
+        <v>0</v>
+      </c>
+      <c r="X9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="7">
         <v>0</v>
       </c>
       <c r="Z9" s="3">
@@ -4476,80 +4536,80 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="24" spans="1:27">
-      <c r="A10" s="5" t="s">
+    <row r="10" ht="20.65" spans="1:27">
+      <c r="A10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="6">
-        <v>1</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0</v>
-      </c>
-      <c r="F10" s="6">
-        <v>0</v>
-      </c>
-      <c r="G10" s="6">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6">
-        <v>0</v>
-      </c>
-      <c r="I10" s="6">
-        <v>0</v>
-      </c>
-      <c r="J10" s="6">
-        <v>0</v>
-      </c>
-      <c r="K10" s="6">
-        <v>0</v>
-      </c>
-      <c r="L10" s="6">
-        <v>0</v>
-      </c>
-      <c r="M10" s="6">
-        <v>0</v>
-      </c>
-      <c r="N10" s="6">
-        <v>0</v>
-      </c>
-      <c r="O10" s="6">
-        <v>0</v>
-      </c>
-      <c r="P10" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>0</v>
-      </c>
-      <c r="R10" s="6">
-        <v>0</v>
-      </c>
-      <c r="S10" s="6">
-        <v>0</v>
-      </c>
-      <c r="T10" s="6">
-        <v>0</v>
-      </c>
-      <c r="U10" s="6">
-        <v>0</v>
-      </c>
-      <c r="V10" s="6">
-        <v>0</v>
-      </c>
-      <c r="W10" s="6">
-        <v>0</v>
-      </c>
-      <c r="X10" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="6">
+      <c r="B10" s="7">
+        <v>1</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7">
+        <v>0</v>
+      </c>
+      <c r="I10" s="7">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0</v>
+      </c>
+      <c r="K10" s="7">
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7">
+        <v>0</v>
+      </c>
+      <c r="N10" s="7">
+        <v>0</v>
+      </c>
+      <c r="O10" s="7">
+        <v>0</v>
+      </c>
+      <c r="P10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7">
+        <v>0</v>
+      </c>
+      <c r="S10" s="7">
+        <v>0</v>
+      </c>
+      <c r="T10" s="7">
+        <v>0</v>
+      </c>
+      <c r="U10" s="7">
+        <v>0</v>
+      </c>
+      <c r="V10" s="7">
+        <v>0</v>
+      </c>
+      <c r="W10" s="7">
+        <v>0</v>
+      </c>
+      <c r="X10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="7">
         <v>0</v>
       </c>
       <c r="Z10" s="3">
@@ -4559,80 +4619,80 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="24" spans="1:27">
-      <c r="A11" s="5" t="s">
+    <row r="11" ht="20.65" spans="1:27">
+      <c r="A11" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>4</v>
       </c>
-      <c r="C11" s="6">
-        <v>0</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7">
         <v>3</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="7">
         <v>3</v>
       </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6">
-        <v>0</v>
-      </c>
-      <c r="I11" s="6">
-        <v>1</v>
-      </c>
-      <c r="J11" s="6">
-        <v>0</v>
-      </c>
-      <c r="K11" s="6">
-        <v>0</v>
-      </c>
-      <c r="L11" s="6">
+      <c r="F11" s="7">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0</v>
+      </c>
+      <c r="I11" s="7">
+        <v>1</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0</v>
+      </c>
+      <c r="K11" s="7">
+        <v>0</v>
+      </c>
+      <c r="L11" s="7">
         <v>10</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="7">
         <v>30</v>
       </c>
-      <c r="N11" s="6">
-        <v>0</v>
-      </c>
-      <c r="O11" s="6">
-        <v>0</v>
-      </c>
-      <c r="P11" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>2</v>
-      </c>
-      <c r="R11" s="6">
+      <c r="N11" s="7">
+        <v>0</v>
+      </c>
+      <c r="O11" s="7">
+        <v>0</v>
+      </c>
+      <c r="P11" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>2</v>
+      </c>
+      <c r="R11" s="7">
         <v>8</v>
       </c>
-      <c r="S11" s="6">
-        <v>0</v>
-      </c>
-      <c r="T11" s="6">
-        <v>2</v>
-      </c>
-      <c r="U11" s="6">
-        <v>0</v>
-      </c>
-      <c r="V11" s="6">
+      <c r="S11" s="7">
+        <v>0</v>
+      </c>
+      <c r="T11" s="7">
+        <v>2</v>
+      </c>
+      <c r="U11" s="7">
+        <v>0</v>
+      </c>
+      <c r="V11" s="7">
         <v>4</v>
       </c>
-      <c r="W11" s="6">
-        <v>0</v>
-      </c>
-      <c r="X11" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="6">
+      <c r="W11" s="7">
+        <v>0</v>
+      </c>
+      <c r="X11" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="7">
         <v>0</v>
       </c>
       <c r="Z11" s="3">
